--- a/Stock_OneClick/history/scan_result_20260529_094204.xlsx
+++ b/Stock_OneClick/history/scan_result_20260529_094204.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -637,24 +637,12 @@
       <c r="J3" s="4" t="n">
         <v>192.94</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-29; 相对D0=7.15%; 本次触发=2026-05-28(预警买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -706,24 +694,12 @@
       <c r="J4" s="4" t="n">
         <v>183.32</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-29; 相对D0=2.21%; 本次触发=2026-05-28(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-28</t>
@@ -775,24 +751,12 @@
       <c r="J5" s="4" t="n">
         <v>308.25</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-29; 相对D0=-5.48%; 本次触发=2026-05-28(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -844,24 +808,12 @@
       <c r="J6" s="4" t="n">
         <v>13.605</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-29; 相对D0=4.49%; 本次触发=2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -913,24 +865,12 @@
       <c r="J7" s="4" t="n">
         <v>112.03</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-05-29; 相对D0=3.57%; 本次触发=2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -982,24 +922,6 @@
       <c r="J8" t="n">
         <v>106.025</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-05-29; 相对D0=0.13%; 本次触发=2026-05-28(预警买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -1051,24 +973,6 @@
       <c r="J9" t="n">
         <v>89.25</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-05-29; 相对D0=0.85%; 本次触发=2026-05-28(预警买入), 2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1120,24 +1024,6 @@
       <c r="J10" t="n">
         <v>162</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-05-29; 相对D0=2.31%; 本次触发=2026-05-28(预警买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1189,24 +1075,12 @@
       <c r="J11" s="4" t="n">
         <v>383.3914</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-05-29; 相对D0=-1.41%; 本次触发=2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -1258,24 +1132,6 @@
       <c r="J12" t="n">
         <v>90.65000000000001</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-05-29; 相对D0=-0.24%; 本次触发=2026-05-28(预警买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -1327,24 +1183,6 @@
       <c r="J13" t="n">
         <v>274.585</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-05-29; 相对D0=-5.32%; 本次触发=2026-05-28(预警买入)</t>
@@ -1396,24 +1234,12 @@
       <c r="J14" s="4" t="n">
         <v>724.0549999999999</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-05-29; 相对D0=7.91%; 本次触发=2026-05-28(预警买入)</t>
@@ -1465,24 +1291,6 @@
       <c r="J15" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-05-29; 相对D0=-0.67%; 本次触发=2026-05-28(预警买入)</t>
@@ -1534,24 +1342,6 @@
       <c r="J16" t="n">
         <v>1065.0625</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-05-29; 相对D0=-0.41%; 本次触发=2026-05-28(预警买入)</t>
@@ -1603,24 +1393,12 @@
       <c r="J17" s="4" t="n">
         <v>135.66</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-05-29; 相对D0=4.60%; 本次触发=2026-05-28(预警买入)</t>
@@ -1672,24 +1450,12 @@
       <c r="J18" s="4" t="n">
         <v>100.775</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-05-29; 相对D0=5.33%; 本次触发=2026-05-28(预警买入)</t>
@@ -1741,24 +1507,12 @@
       <c r="J19" s="4" t="n">
         <v>444.465</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-05-29; 相对D0=4.09%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -1810,24 +1564,6 @@
       <c r="J20" t="n">
         <v>223.57</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-05-29; 相对D0=-1.22%; 本次触发=2026-05-28(预警买入)</t>
@@ -1879,24 +1615,12 @@
       <c r="J21" s="4" t="n">
         <v>121.085</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-05-29; 相对D0=27.83%; 本次触发=2026-05-28(预警买入)</t>
@@ -1948,24 +1672,12 @@
       <c r="J22" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="K22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-05-29; 相对D0=6.68%; 本次触发=2026-05-28(预警买入)</t>
@@ -2017,24 +1729,12 @@
       <c r="J23" s="4" t="n">
         <v>156.3</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-05-29; 相对D0=9.04%; 本次触发=2026-05-28(二进宫买入点 | 正式买入 | 预警买入)</t>
@@ -2086,27 +1786,15 @@
       <c r="J24" s="4" t="n">
         <v>255.41</v>
       </c>
-      <c r="K24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>D0=255.41; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=255.41; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -2155,24 +1843,12 @@
       <c r="J25" s="4" t="n">
         <v>287.85</v>
       </c>
-      <c r="K25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>D0=287.85; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入)</t>
@@ -2224,24 +1900,12 @@
       <c r="J26" s="4" t="n">
         <v>217.31</v>
       </c>
-      <c r="K26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>D0=217.31; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -2293,24 +1957,6 @@
       <c r="J27" t="n">
         <v>154.025</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-29; 相对D0=-15.13%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2362,24 +2008,12 @@
       <c r="J28" s="4" t="n">
         <v>197.715</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-29; 相对D0=-2.56%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2431,24 +2065,12 @@
       <c r="J29" s="4" t="n">
         <v>170.68</v>
       </c>
-      <c r="K29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-29; 相对D0=1.98%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2500,24 +2122,12 @@
       <c r="J30" s="4" t="n">
         <v>53.025</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-29; 相对D0=13.96%</t>
@@ -2569,24 +2179,6 @@
       <c r="J31" t="n">
         <v>16.635</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-29; 相对D0=3.19%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2638,24 +2230,12 @@
       <c r="J32" s="4" t="n">
         <v>47.935</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-29; 相对D0=-0.38%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2707,24 +2287,6 @@
       <c r="J33" t="n">
         <v>132.47</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-29; 相对D0=-6.20%</t>
@@ -2776,24 +2338,6 @@
       <c r="J34" t="n">
         <v>399.255</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-29; 相对D0=2.02%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2845,24 +2389,6 @@
       <c r="J35" t="n">
         <v>964.02</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-29; 相对D0=-7.19%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2914,24 +2440,6 @@
       <c r="J36" t="n">
         <v>24.12</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-29; 相对D0=7.15%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2983,24 +2491,6 @@
       <c r="J37" t="n">
         <v>250.34</v>
       </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-29; 相对D0=7.91%</t>
@@ -3052,24 +2542,6 @@
       <c r="J38" t="n">
         <v>151.8</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-29; 相对D0=16.32%</t>
@@ -3121,24 +2593,12 @@
       <c r="J39" s="4" t="n">
         <v>256.4499</v>
       </c>
-      <c r="K39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-29; 相对D0=-2.21%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -3190,24 +2650,12 @@
       <c r="J40" s="4" t="n">
         <v>104.5799</v>
       </c>
-      <c r="K40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-29; 相对D0=22.43%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3259,24 +2707,12 @@
       <c r="J41" s="4" t="n">
         <v>437.96</v>
       </c>
-      <c r="K41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-29; 相对D0=2.81%</t>
@@ -3328,24 +2764,12 @@
       <c r="J42" s="4" t="n">
         <v>69.25</v>
       </c>
-      <c r="K42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-05-29; 相对D0=-5.73%</t>
@@ -3397,24 +2821,6 @@
       <c r="J43" t="n">
         <v>440.8846</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-05-29; 相对D0=4.47%</t>
@@ -3466,24 +2872,6 @@
       <c r="J44" t="n">
         <v>88.605</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-05-29; 相对D0=2.45%</t>
@@ -3535,24 +2923,12 @@
       <c r="J45" s="4" t="n">
         <v>624.51</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-05-29; 相对D0=1.99%</t>
@@ -3604,24 +2980,12 @@
       <c r="J46" s="4" t="n">
         <v>68.66</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-05-29; 相对D0=-0.06%</t>
@@ -3673,24 +3037,6 @@
       <c r="J47" t="n">
         <v>106.825</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-05-29; 相对D0=-0.11%</t>
@@ -3742,24 +3088,12 @@
       <c r="J48" s="4" t="n">
         <v>12.58</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-05-29; 相对D0=2.95%</t>
@@ -3811,24 +3145,6 @@
       <c r="J49" t="n">
         <v>84.98</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-05-29; 相对D0=0.40%</t>
@@ -3880,24 +3196,12 @@
       <c r="J50" s="4" t="n">
         <v>18.061</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-05-29; 相对D0=-1.84%</t>
@@ -3949,24 +3253,6 @@
       <c r="J51" t="n">
         <v>312.23</v>
       </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
-      <c r="L51" t="n">
-        <v/>
-      </c>
-      <c r="M51" t="n">
-        <v/>
-      </c>
-      <c r="N51" t="n">
-        <v/>
-      </c>
-      <c r="O51" t="n">
-        <v/>
-      </c>
-      <c r="P51" t="n">
-        <v/>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-05-29; 相对D0=-3.61%</t>
@@ -4018,24 +3304,12 @@
       <c r="J52" s="4" t="n">
         <v>272.0579</v>
       </c>
-      <c r="K52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-05-29; 相对D0=0.08%</t>
@@ -4087,24 +3361,6 @@
       <c r="J53" t="n">
         <v>35.75</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-05-29; 相对D0=-13.54%</t>
@@ -4156,24 +3412,12 @@
       <c r="J54" s="4" t="n">
         <v>123.8375</v>
       </c>
-      <c r="K54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-05-29; 相对D0=21.27%</t>
@@ -4224,24 +3468,6 @@
       </c>
       <c r="J55" t="n">
         <v>222.38</v>
-      </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4479,24 +3705,12 @@
       <c r="J67" s="4" t="n">
         <v>102.33</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-05-29; 相对D0=-11.56%; 本次触发=2026-05-28(正式卖出)</t>
@@ -4548,24 +3762,12 @@
       <c r="J68" s="4" t="n">
         <v>287.85</v>
       </c>
-      <c r="K68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-05-29; 相对D0=0.54%; 本次触发=2026-05-28(正式卖出)</t>
@@ -4617,24 +3819,12 @@
       <c r="J69" s="4" t="n">
         <v>176.26</v>
       </c>
-      <c r="K69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-05-29; 相对D0=-3.67%; 本次触发=2026-05-28(正式卖出)</t>
@@ -4686,24 +3876,12 @@
       <c r="J70" s="4" t="n">
         <v>477.31</v>
       </c>
-      <c r="K70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-05-29; 相对D0=-0.69%; 本次触发=2026-05-28(正式卖出 | 预警卖出)</t>
@@ -4755,24 +3933,6 @@
       <c r="J71" t="n">
         <v>69.25</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=69.25; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4824,24 +3984,12 @@
       <c r="J72" s="4" t="n">
         <v>274.49</v>
       </c>
-      <c r="K72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>D0=274.49; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -4893,24 +4041,12 @@
       <c r="J73" s="4" t="n">
         <v>348.81</v>
       </c>
-      <c r="K73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>D0=348.81; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -4962,24 +4098,12 @@
       <c r="J74" s="4" t="n">
         <v>19.205</v>
       </c>
-      <c r="K74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>D0=19.20; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -5031,24 +4155,6 @@
       <c r="J75" t="n">
         <v>135.15</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=135.15; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -5100,24 +4206,12 @@
       <c r="J76" s="4" t="n">
         <v>249.51</v>
       </c>
-      <c r="K76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P76" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>D0=249.51; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -5169,24 +4263,12 @@
       <c r="J77" s="4" t="n">
         <v>38.8</v>
       </c>
-      <c r="K77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-29; 相对D0=-6.44%</t>
@@ -5238,24 +4320,6 @@
       <c r="J78" t="n">
         <v>90.66</v>
       </c>
-      <c r="K78" t="n">
-        <v/>
-      </c>
-      <c r="L78" t="n">
-        <v/>
-      </c>
-      <c r="M78" t="n">
-        <v/>
-      </c>
-      <c r="N78" t="n">
-        <v/>
-      </c>
-      <c r="O78" t="n">
-        <v/>
-      </c>
-      <c r="P78" t="n">
-        <v/>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-05-29; 相对D0=0.02%</t>
@@ -5307,24 +4371,12 @@
       <c r="J79" s="4" t="n">
         <v>181.53</v>
       </c>
-      <c r="K79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-05-29; 相对D0=-1.72%</t>
@@ -5376,24 +4428,12 @@
       <c r="J80" s="4" t="n">
         <v>132.47</v>
       </c>
-      <c r="K80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P80" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-05-29; 相对D0=-2.74%</t>
@@ -5445,24 +4485,6 @@
       <c r="J81" t="n">
         <v>35.75</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-05-29; 相对D0=-4.95%</t>
@@ -5514,24 +4536,6 @@
       <c r="J82" t="n">
         <v>308.25</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-05-29; 相对D0=0.29%</t>
@@ -5583,24 +4587,12 @@
       <c r="J83" s="4" t="n">
         <v>56.35</v>
       </c>
-      <c r="K83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-05-29; 相对D0=-1.93%</t>
@@ -5652,24 +4644,12 @@
       <c r="J84" s="4" t="n">
         <v>12.2786</v>
       </c>
-      <c r="K84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-05-29; 相对D0=-8.03%</t>
@@ -5721,24 +4701,12 @@
       <c r="J85" s="4" t="n">
         <v>55.07</v>
       </c>
-      <c r="K85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-05-29; 相对D0=-2.53%</t>
@@ -5789,24 +4757,6 @@
       </c>
       <c r="J86" t="n">
         <v>137.81</v>
-      </c>
-      <c r="K86" t="n">
-        <v/>
-      </c>
-      <c r="L86" t="n">
-        <v/>
-      </c>
-      <c r="M86" t="n">
-        <v/>
-      </c>
-      <c r="N86" t="n">
-        <v/>
-      </c>
-      <c r="O86" t="n">
-        <v/>
-      </c>
-      <c r="P86" t="n">
-        <v/>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -5904,7 +4854,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5916,7 +4865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6461,10 +5410,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6476,7 +5421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6760,7 +5705,6 @@
       <c r="G9" s="13" t="n">
         <v>0.040926</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6792,7 +5736,6 @@
       <c r="G10" s="12" t="n">
         <v>-0.012238</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7222,9 +6165,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7236,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7304,7 +6244,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -7701,8 +6641,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8431,8 +7369,6 @@
       <c r="T8" t="b">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.99; 4H分金=40.47</t>
@@ -8601,8 +7537,6 @@
       <c r="T10" t="b">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=48.46; 4H分金=56.39</t>
@@ -8858,8 +7792,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=47.24; 4H分金=41.94</t>
@@ -9028,8 +7960,6 @@
       <c r="T15" t="b">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.03; 4H分金=50.55</t>
@@ -9111,8 +8041,6 @@
       <c r="T16" t="b">
         <v>0</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=43.14; 4H分金=47.96</t>
@@ -10888,7 +9816,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13370,8 +12298,6 @@
       <c r="T65" t="b">
         <v>1</v>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.74; 4H分金=44.00</t>
@@ -13584,7 +12510,6 @@
       <c r="D3" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46170</v>
       </c>
@@ -13636,7 +12561,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -13842,7 +12766,6 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" s="8" t="n">
         <v>46171</v>
       </c>
@@ -13954,7 +12877,6 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" s="8" t="n">
         <v>46169</v>
       </c>
@@ -14043,7 +12965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14563,7 +13485,6 @@
       <c r="M10" s="12" t="n">
         <v>-0.06196</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -14883,7 +13804,6 @@
       <c r="M16" s="13" t="n">
         <v>0.079052</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14933,7 +13853,6 @@
       <c r="M17" s="13" t="n">
         <v>0.163218</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -15091,7 +14010,6 @@
       <c r="M20" s="13" t="n">
         <v>0.028051</v>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -15405,11 +14323,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15421,7 +14334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15582,24 +14495,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15651,24 +14552,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15720,24 +14609,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15789,24 +14666,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15858,24 +14723,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15927,24 +14774,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15996,24 +14831,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16065,24 +14888,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16134,24 +14939,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16203,24 +14996,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16272,24 +15053,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16341,24 +15110,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16410,24 +15167,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16479,24 +15218,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16548,24 +15269,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16617,24 +15320,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16686,24 +15377,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16755,24 +15434,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -16824,24 +15485,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -17078,24 +15727,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -17140,11 +15777,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17156,7 +15788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17328,7 +15960,6 @@
       <c r="K4" s="13" t="n">
         <v>0.044725</v>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -17676,7 +16307,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -17764,7 +16395,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -17832,7 +16463,6 @@
       <c r="K15" s="13" t="n">
         <v>0.004017</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -17920,7 +16550,6 @@
       <c r="K17" s="12" t="n">
         <v>-0.036059</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -18480,7 +17109,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
